--- a/GSU_Cayuse_Lite.xlsx
+++ b/GSU_Cayuse_Lite.xlsx
@@ -1423,7 +1423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2229,6 +2229,261 @@
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>Upload letter</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TSK-0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GSU-P-0004</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Complete GSU Internal Routing Form</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Attach signed PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TSK-0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GSU-P-0004</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COI Disclosures for all key personnel</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PI/OSP</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TSK-0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GSU-P-0004</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Subrecipient Commitment Form(s)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>OSP</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Collect UEI and F&amp;A rate docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TSK-0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GSU-P-0004</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Export Control &amp; Data Security review</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>If foreign collaborators or controlled data</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TSK-0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GSU-P-0004</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Final Budget &amp; Justification</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OSP Pre-Award</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Check salary cap and F&amp;A base</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TSK-0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GSU-P-0004</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Create application in Research.gov</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OSP Pre-Award</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Confirm FOA &amp; forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TSK-0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GSU-P-0004</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dean/Provost cost-share letter (if required)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Dean/Provost</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Upload letter</t>
         </is>
@@ -2648,7 +2903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AF5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3175,6 +3430,114 @@
       <c r="AF4" t="inlineStr">
         <is>
           <t>Imported by BrassLoom on 2025-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GSU-P-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MPS Astronomical Sciences Research Programs (MPS Astro)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NSF Funding</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Federal</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.nsf.gov/funding/opportunities/mps-astro-mps-astronomical-sciences-research-programs</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Research.gov</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Department Review</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Imported by BrassLoom on 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/GSU_Cayuse_Lite.xlsx
+++ b/GSU_Cayuse_Lite.xlsx
@@ -2302,7 +2302,6 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3444,11 +3443,6 @@
           <t>MPS Astronomical Sciences Research Programs (MPS Astro)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>NSF Funding</t>
@@ -3489,19 +3483,11 @@
           <t>Department Review</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
           <t>No</t>
